--- a/tests/report/selenium-test-results.xlsx
+++ b/tests/report/selenium-test-results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="88">
   <si>
     <t>Test ID</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.064Z</t>
+    <t>2026-06-13T07:08:39.802Z</t>
   </si>
   <si>
     <t>Preview works</t>
@@ -52,7 +52,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.065Z</t>
+    <t>2026-06-13T07:08:39.805Z</t>
   </si>
   <si>
     <t>HTTPS backend</t>
@@ -67,7 +67,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.067Z</t>
+    <t>2026-06-13T07:08:43.381Z</t>
   </si>
   <si>
     <t>UI/UX</t>
@@ -79,7 +79,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.080Z</t>
+    <t>2026-06-13T07:08:43.396Z</t>
   </si>
   <si>
     <t>Features render</t>
@@ -88,7 +88,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.092Z</t>
+    <t>2026-06-13T07:08:43.411Z</t>
   </si>
   <si>
     <t>CTAs visible</t>
@@ -97,7 +97,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.102Z</t>
+    <t>2026-06-13T07:08:43.428Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -106,7 +106,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.116Z</t>
+    <t>2026-06-13T07:08:43.443Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -118,7 +118,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.275Z</t>
+    <t>2026-06-13T07:08:43.603Z</t>
   </si>
   <si>
     <t>Dashboard route</t>
@@ -133,7 +133,7 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.345Z</t>
+    <t>2026-06-13T07:08:43.674Z</t>
   </si>
   <si>
     <t>Dashboard cards</t>
@@ -142,7 +142,7 @@
     <t>Found 16 cards</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.372Z</t>
+    <t>2026-06-13T07:08:43.688Z</t>
   </si>
   <si>
     <t>Jobs route</t>
@@ -151,7 +151,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.483Z</t>
+    <t>2026-06-13T07:08:43.824Z</t>
   </si>
   <si>
     <t>Search input</t>
@@ -160,7 +160,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.869Z</t>
+    <t>2026-06-13T07:08:43.861Z</t>
   </si>
   <si>
     <t>Filters visible</t>
@@ -169,7 +169,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.880Z</t>
+    <t>2026-06-13T07:08:43.871Z</t>
   </si>
   <si>
     <t>Search works</t>
@@ -178,25 +178,28 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.899Z</t>
+    <t>2026-06-13T07:08:44.879Z</t>
   </si>
   <si>
     <t>Job grid</t>
   </si>
   <si>
-    <t>Found 6 jobs</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.915Z</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Found 0 jobs</t>
+  </si>
+  <si>
+    <t>2026-06-13T07:08:54.943Z</t>
   </si>
   <si>
     <t>Apply buttons</t>
   </si>
   <si>
-    <t>Found 6 buttons</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.925Z</t>
+    <t>Found 0 buttons</t>
+  </si>
+  <si>
+    <t>2026-06-13T07:08:54.955Z</t>
   </si>
   <si>
     <t>Validation</t>
@@ -208,7 +211,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.946Z</t>
+    <t>2026-06-13T07:08:54.988Z</t>
   </si>
   <si>
     <t>No results</t>
@@ -217,7 +220,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.129Z</t>
+    <t>2026-06-13T07:08:56.120Z</t>
   </si>
   <si>
     <t>Analytics route</t>
@@ -226,7 +229,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.202Z</t>
+    <t>2026-06-13T07:08:56.217Z</t>
   </si>
   <si>
     <t>Mobile layout</t>
@@ -235,7 +238,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:23.774Z</t>
+    <t>2026-06-13T07:08:57.804Z</t>
   </si>
   <si>
     <t>Desktop layout</t>
@@ -244,16 +247,16 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:24.717Z</t>
+    <t>2026-06-13T07:08:58.966Z</t>
   </si>
   <si>
     <t>API works</t>
   </si>
   <si>
-    <t>100 jobs returned</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:25.300Z</t>
+    <t>fetch failed</t>
+  </si>
+  <si>
+    <t>2026-06-13T07:09:09.682Z</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -262,190 +265,18 @@
     <t>Routes work</t>
   </si>
   <si>
-    <t>Refresh works</t>
-  </si>
-  <si>
-    <t>Page refresh succeeds</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:25.865Z</t>
-  </si>
-  <si>
-    <t>SPA routing</t>
-  </si>
-  <si>
-    <t>Client-side routing</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:26.866Z</t>
-  </si>
-  <si>
-    <t>Static ready</t>
-  </si>
-  <si>
-    <t>Build is static</t>
-  </si>
-  <si>
-    <t>Accessibility</t>
-  </si>
-  <si>
-    <t>Inputs accessible</t>
-  </si>
-  <si>
-    <t>Search found</t>
-  </si>
-  <si>
-    <t>Keyboard nav</t>
-  </si>
-  <si>
-    <t>Keyboard support</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:26.867Z</t>
-  </si>
-  <si>
-    <t>Contrast good</t>
-  </si>
-  <si>
-    <t>UI readable</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Home renders</t>
-  </si>
-  <si>
-    <t>Component loads</t>
-  </si>
-  <si>
-    <t>JobCard renders</t>
-  </si>
-  <si>
-    <t>Cards display</t>
-  </si>
-  <si>
-    <t>JobContext</t>
-  </si>
-  <si>
-    <t>State works</t>
-  </si>
-  <si>
-    <t>Navbar</t>
-  </si>
-  <si>
-    <t>Nav renders</t>
-  </si>
-  <si>
-    <t>Empty handling</t>
-  </si>
-  <si>
-    <t>No-results works</t>
-  </si>
-  <si>
-    <t>External links</t>
-  </si>
-  <si>
-    <t>Links safe</t>
-  </si>
-  <si>
-    <t>Filter stability</t>
-  </si>
-  <si>
-    <t>Filters stable</t>
-  </si>
-  <si>
-    <t>Interactive</t>
-  </si>
-  <si>
-    <t>UI responsive</t>
-  </si>
-  <si>
-    <t>SPA nav</t>
-  </si>
-  <si>
-    <t>No reloads</t>
-  </si>
-  <si>
-    <t>Form labels</t>
-  </si>
-  <si>
-    <t>Inputs labeled</t>
-  </si>
-  <si>
-    <t>Headings</t>
-  </si>
-  <si>
-    <t>Hierarchy correct</t>
-  </si>
-  <si>
-    <t>Charts</t>
-  </si>
-  <si>
-    <t>Analytics show</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Header sticky</t>
-  </si>
-  <si>
-    <t>Hover states</t>
-  </si>
-  <si>
-    <t>Feedback works</t>
-  </si>
-  <si>
-    <t>Contrast</t>
-  </si>
-  <si>
-    <t>Readable</t>
-  </si>
-  <si>
-    <t>Badges</t>
-  </si>
-  <si>
-    <t>Indicators show</t>
-  </si>
-  <si>
-    <t>Location filter</t>
-  </si>
-  <si>
-    <t>Filter present</t>
-  </si>
-  <si>
-    <t>Skill filter</t>
-  </si>
-  <si>
-    <t>Clear filters</t>
-  </si>
-  <si>
-    <t>Reset works</t>
-  </si>
-  <si>
-    <t>Search state</t>
-  </si>
-  <si>
-    <t>State updates</t>
-  </si>
-  <si>
-    <t>Layout stability</t>
-  </si>
-  <si>
-    <t>No shift</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Loads quick</t>
-  </si>
-  <si>
-    <t>Dashboard data</t>
-  </si>
-  <si>
-    <t>Data renders</t>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Fatal error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid session id: session deleted as the browser has closed the connection
+from disconnected: not connected to DevTools
+  (Session info: chrome=148.0.7778.179)</t>
+  </si>
+  <si>
+    <t>2026-06-13T07:09:09.685Z</t>
   </si>
 </sst>
 </file>
@@ -822,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1184,13 +1015,13 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1201,16 +1032,16 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1218,19 +1049,19 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1241,16 +1072,16 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1261,16 +1092,16 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1281,16 +1112,16 @@
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1301,16 +1132,16 @@
         <v>19</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1321,16 +1152,16 @@
         <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,596 +1172,36 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" t="s">
         <v>81</v>
-      </c>
-      <c r="D26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>95</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" t="s">
-        <v>86</v>
-      </c>
-      <c r="D28" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" t="s">
         <v>87</v>
-      </c>
-      <c r="F28" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>98</v>
-      </c>
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>101</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>102</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>104</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" t="s">
-        <v>98</v>
-      </c>
-      <c r="F32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>71</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
-      </c>
-      <c r="F33" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>73</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>75</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" t="s">
-        <v>105</v>
-      </c>
-      <c r="F35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>76</v>
-      </c>
-      <c r="B36" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" t="s">
-        <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" t="s">
-        <v>107</v>
-      </c>
-      <c r="F36" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>50</v>
-      </c>
-      <c r="B37" t="s">
-        <v>62</v>
-      </c>
-      <c r="C37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" t="s">
-        <v>109</v>
-      </c>
-      <c r="F37" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>54</v>
-      </c>
-      <c r="B38" t="s">
-        <v>62</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F38" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>55</v>
-      </c>
-      <c r="B39" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" t="s">
-        <v>115</v>
-      </c>
-      <c r="F40" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>66</v>
-      </c>
-      <c r="B41" t="s">
-        <v>62</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>67</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>19</v>
-      </c>
-      <c r="C43" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>10</v>
-      </c>
-      <c r="B44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" t="s">
-        <v>123</v>
-      </c>
-      <c r="F44" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" t="s">
-        <v>125</v>
-      </c>
-      <c r="F45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>12</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" t="s">
-        <v>127</v>
-      </c>
-      <c r="F46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>13</v>
-      </c>
-      <c r="B47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C47" t="s">
-        <v>128</v>
-      </c>
-      <c r="D47" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" t="s">
-        <v>129</v>
-      </c>
-      <c r="F47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" t="s">
-        <v>131</v>
-      </c>
-      <c r="F48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>21</v>
-      </c>
-      <c r="B49" t="s">
-        <v>32</v>
-      </c>
-      <c r="C49" t="s">
-        <v>132</v>
-      </c>
-      <c r="D49" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" t="s">
-        <v>133</v>
-      </c>
-      <c r="F49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>22</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50" t="s">
-        <v>134</v>
-      </c>
-      <c r="D50" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" t="s">
-        <v>133</v>
-      </c>
-      <c r="F50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>23</v>
-      </c>
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-      <c r="C51" t="s">
-        <v>135</v>
-      </c>
-      <c r="D51" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" t="s">
-        <v>136</v>
-      </c>
-      <c r="F51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>32</v>
-      </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>137</v>
-      </c>
-      <c r="D52" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" t="s">
-        <v>138</v>
-      </c>
-      <c r="F52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>40</v>
-      </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" t="s">
-        <v>139</v>
-      </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" t="s">
-        <v>140</v>
-      </c>
-      <c r="F53" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>44</v>
-      </c>
-      <c r="B54" t="s">
-        <v>32</v>
-      </c>
-      <c r="C54" t="s">
-        <v>141</v>
-      </c>
-      <c r="D54" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" t="s">
-        <v>142</v>
-      </c>
-      <c r="F54" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>69</v>
-      </c>
-      <c r="B55" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" t="s">
-        <v>143</v>
-      </c>
-      <c r="D55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" t="s">
-        <v>144</v>
-      </c>
-      <c r="F55" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/tests/report/selenium-test-results.xlsx
+++ b/tests/report/selenium-test-results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="144">
   <si>
     <t>Test ID</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.064Z</t>
+    <t>2026-06-13T08:19:11.417Z</t>
   </si>
   <si>
     <t>Preview works</t>
@@ -52,7 +52,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:16.065Z</t>
+    <t>2026-06-13T08:19:11.418Z</t>
   </si>
   <si>
     <t>HTTPS backend</t>
@@ -67,7 +67,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.067Z</t>
+    <t>2026-06-13T08:19:14.732Z</t>
   </si>
   <si>
     <t>UI/UX</t>
@@ -79,7 +79,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.080Z</t>
+    <t>2026-06-13T08:19:14.752Z</t>
   </si>
   <si>
     <t>Features render</t>
@@ -88,7 +88,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.092Z</t>
+    <t>2026-06-13T08:19:14.772Z</t>
   </si>
   <si>
     <t>CTAs visible</t>
@@ -97,7 +97,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.102Z</t>
+    <t>2026-06-13T08:19:14.790Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -106,7 +106,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.116Z</t>
+    <t>2026-06-13T08:19:14.808Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -118,7 +118,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.275Z</t>
+    <t>2026-06-13T08:19:15.049Z</t>
   </si>
   <si>
     <t>Dashboard route</t>
@@ -133,16 +133,16 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.345Z</t>
+    <t>2026-06-13T08:19:15.512Z</t>
   </si>
   <si>
     <t>Dashboard cards</t>
   </si>
   <si>
-    <t>Found 16 cards</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:19.372Z</t>
+    <t>Found 19 cards</t>
+  </si>
+  <si>
+    <t>2026-06-13T08:19:15.531Z</t>
   </si>
   <si>
     <t>Jobs route</t>
@@ -151,7 +151,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.483Z</t>
+    <t>2026-06-13T08:19:15.765Z</t>
   </si>
   <si>
     <t>Search input</t>
@@ -160,7 +160,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.869Z</t>
+    <t>2026-06-13T08:19:16.081Z</t>
   </si>
   <si>
     <t>Filters visible</t>
@@ -169,7 +169,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:19.880Z</t>
+    <t>2026-06-13T08:19:16.096Z</t>
   </si>
   <si>
     <t>Search works</t>
@@ -178,25 +178,25 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.899Z</t>
+    <t>2026-06-13T08:19:17.238Z</t>
   </si>
   <si>
     <t>Job grid</t>
   </si>
   <si>
-    <t>Found 6 jobs</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.915Z</t>
+    <t>Found 5 jobs</t>
+  </si>
+  <si>
+    <t>2026-06-13T08:19:17.262Z</t>
   </si>
   <si>
     <t>Apply buttons</t>
   </si>
   <si>
-    <t>Found 6 buttons</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:20.925Z</t>
+    <t>Found 5 buttons</t>
+  </si>
+  <si>
+    <t>2026-06-13T08:19:17.276Z</t>
   </si>
   <si>
     <t>Validation</t>
@@ -208,7 +208,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:20.946Z</t>
+    <t>2026-06-13T08:19:17.311Z</t>
   </si>
   <si>
     <t>No results</t>
@@ -217,7 +217,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.129Z</t>
+    <t>2026-06-13T08:19:18.644Z</t>
   </si>
   <si>
     <t>Analytics route</t>
@@ -226,7 +226,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:22.202Z</t>
+    <t>2026-06-13T08:19:18.724Z</t>
   </si>
   <si>
     <t>Mobile layout</t>
@@ -235,7 +235,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:23.774Z</t>
+    <t>2026-06-13T08:19:20.299Z</t>
   </si>
   <si>
     <t>Desktop layout</t>
@@ -244,7 +244,7 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:24.717Z</t>
+    <t>2026-06-13T08:19:21.138Z</t>
   </si>
   <si>
     <t>API works</t>
@@ -253,7 +253,7 @@
     <t>100 jobs returned</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:25.300Z</t>
+    <t>2026-06-13T08:19:21.983Z</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -268,7 +268,7 @@
     <t>Page refresh succeeds</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:25.865Z</t>
+    <t>2026-06-13T08:19:22.316Z</t>
   </si>
   <si>
     <t>SPA routing</t>
@@ -277,7 +277,7 @@
     <t>Client-side routing</t>
   </si>
   <si>
-    <t>2026-06-12T08:48:26.866Z</t>
+    <t>2026-06-13T08:19:23.320Z</t>
   </si>
   <si>
     <t>Static ready</t>
@@ -299,9 +299,6 @@
   </si>
   <si>
     <t>Keyboard support</t>
-  </si>
-  <si>
-    <t>2026-06-12T08:48:26.867Z</t>
   </si>
   <si>
     <t>Contrast good</t>
@@ -1450,7 +1447,7 @@
         <v>95</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1461,16 +1458,16 @@
         <v>91</v>
       </c>
       <c r="C32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
         <v>97</v>
       </c>
-      <c r="D32" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" t="s">
-        <v>98</v>
-      </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,19 +1475,19 @@
         <v>71</v>
       </c>
       <c r="B33" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" t="s">
         <v>99</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
         <v>100</v>
       </c>
-      <c r="D33" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
-      </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,19 +1495,19 @@
         <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
         <v>102</v>
       </c>
-      <c r="D34" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" t="s">
-        <v>103</v>
-      </c>
       <c r="F34" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,19 +1515,19 @@
         <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
         <v>104</v>
       </c>
-      <c r="D35" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" t="s">
-        <v>105</v>
-      </c>
       <c r="F35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1538,19 +1535,19 @@
         <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
         <v>106</v>
       </c>
-      <c r="D36" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" t="s">
-        <v>107</v>
-      </c>
       <c r="F36" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,16 +1558,16 @@
         <v>62</v>
       </c>
       <c r="C37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="s">
         <v>108</v>
       </c>
-      <c r="D37" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" t="s">
-        <v>109</v>
-      </c>
       <c r="F37" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1581,16 +1578,16 @@
         <v>62</v>
       </c>
       <c r="C38" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
         <v>110</v>
       </c>
-      <c r="D38" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1601,16 +1598,16 @@
         <v>62</v>
       </c>
       <c r="C39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
         <v>112</v>
       </c>
-      <c r="D39" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" t="s">
-        <v>113</v>
-      </c>
       <c r="F39" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,16 +1618,16 @@
         <v>62</v>
       </c>
       <c r="C40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
         <v>114</v>
       </c>
-      <c r="D40" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" t="s">
-        <v>115</v>
-      </c>
       <c r="F40" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1641,16 +1638,16 @@
         <v>62</v>
       </c>
       <c r="C41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
         <v>116</v>
       </c>
-      <c r="D41" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" t="s">
-        <v>117</v>
-      </c>
       <c r="F41" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1661,16 +1658,16 @@
         <v>62</v>
       </c>
       <c r="C42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
         <v>118</v>
       </c>
-      <c r="D42" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" t="s">
-        <v>119</v>
-      </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1681,16 +1678,16 @@
         <v>19</v>
       </c>
       <c r="C43" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
         <v>120</v>
       </c>
-      <c r="D43" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" t="s">
-        <v>121</v>
-      </c>
       <c r="F43" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1701,16 +1698,16 @@
         <v>19</v>
       </c>
       <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="s">
         <v>122</v>
       </c>
-      <c r="D44" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" t="s">
-        <v>123</v>
-      </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1721,16 +1718,16 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="s">
         <v>124</v>
       </c>
-      <c r="D45" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" t="s">
-        <v>125</v>
-      </c>
       <c r="F45" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,16 +1738,16 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" t="s">
         <v>126</v>
       </c>
-      <c r="D46" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" t="s">
-        <v>127</v>
-      </c>
       <c r="F46" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1761,16 +1758,16 @@
         <v>19</v>
       </c>
       <c r="C47" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" t="s">
         <v>128</v>
       </c>
-      <c r="D47" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" t="s">
-        <v>129</v>
-      </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1781,16 +1778,16 @@
         <v>19</v>
       </c>
       <c r="C48" t="s">
+        <v>129</v>
+      </c>
+      <c r="D48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" t="s">
         <v>130</v>
       </c>
-      <c r="D48" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" t="s">
-        <v>131</v>
-      </c>
       <c r="F48" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1801,16 +1798,16 @@
         <v>32</v>
       </c>
       <c r="C49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
         <v>132</v>
       </c>
-      <c r="D49" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" t="s">
-        <v>133</v>
-      </c>
       <c r="F49" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,16 +1818,16 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1841,16 +1838,16 @@
         <v>32</v>
       </c>
       <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" t="s">
         <v>135</v>
       </c>
-      <c r="D51" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" t="s">
-        <v>136</v>
-      </c>
       <c r="F51" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1861,16 +1858,16 @@
         <v>32</v>
       </c>
       <c r="C52" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="s">
         <v>137</v>
       </c>
-      <c r="D52" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" t="s">
-        <v>138</v>
-      </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1881,16 +1878,16 @@
         <v>32</v>
       </c>
       <c r="C53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" t="s">
         <v>139</v>
       </c>
-      <c r="D53" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" t="s">
-        <v>140</v>
-      </c>
       <c r="F53" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1901,16 +1898,16 @@
         <v>32</v>
       </c>
       <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="s">
         <v>141</v>
       </c>
-      <c r="D54" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" t="s">
-        <v>142</v>
-      </c>
       <c r="F54" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1921,16 +1918,16 @@
         <v>32</v>
       </c>
       <c r="C55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" t="s">
         <v>143</v>
       </c>
-      <c r="D55" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" t="s">
-        <v>144</v>
-      </c>
       <c r="F55" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/tests/report/selenium-test-results.xlsx
+++ b/tests/report/selenium-test-results.xlsx
@@ -43,7 +43,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:11.417Z</t>
+    <t>2026-06-13T08:46:34.374Z</t>
   </si>
   <si>
     <t>Preview works</t>
@@ -52,7 +52,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:11.418Z</t>
+    <t>2026-06-13T08:46:34.385Z</t>
   </si>
   <si>
     <t>HTTPS backend</t>
@@ -67,7 +67,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:14.732Z</t>
+    <t>2026-06-13T08:46:37.228Z</t>
   </si>
   <si>
     <t>UI/UX</t>
@@ -79,7 +79,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:14.752Z</t>
+    <t>2026-06-13T08:46:37.255Z</t>
   </si>
   <si>
     <t>Features render</t>
@@ -88,7 +88,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:14.772Z</t>
+    <t>2026-06-13T08:46:37.279Z</t>
   </si>
   <si>
     <t>CTAs visible</t>
@@ -97,7 +97,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:14.790Z</t>
+    <t>2026-06-13T08:46:37.305Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -106,7 +106,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:14.808Z</t>
+    <t>2026-06-13T08:46:37.327Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -118,7 +118,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:15.049Z</t>
+    <t>2026-06-13T08:46:37.642Z</t>
   </si>
   <si>
     <t>Dashboard route</t>
@@ -133,16 +133,16 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:15.512Z</t>
+    <t>2026-06-13T08:46:38.259Z</t>
   </si>
   <si>
     <t>Dashboard cards</t>
   </si>
   <si>
-    <t>Found 19 cards</t>
-  </si>
-  <si>
-    <t>2026-06-13T08:19:15.531Z</t>
+    <t>Found 20 cards</t>
+  </si>
+  <si>
+    <t>2026-06-13T08:46:38.286Z</t>
   </si>
   <si>
     <t>Jobs route</t>
@@ -151,7 +151,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:15.765Z</t>
+    <t>2026-06-13T08:46:38.765Z</t>
   </si>
   <si>
     <t>Search input</t>
@@ -160,7 +160,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:16.081Z</t>
+    <t>2026-06-13T08:46:39.175Z</t>
   </si>
   <si>
     <t>Filters visible</t>
@@ -169,7 +169,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:16.096Z</t>
+    <t>2026-06-13T08:46:39.204Z</t>
   </si>
   <si>
     <t>Search works</t>
@@ -178,7 +178,7 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:17.238Z</t>
+    <t>2026-06-13T08:46:40.426Z</t>
   </si>
   <si>
     <t>Job grid</t>
@@ -187,7 +187,7 @@
     <t>Found 5 jobs</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:17.262Z</t>
+    <t>2026-06-13T08:46:40.458Z</t>
   </si>
   <si>
     <t>Apply buttons</t>
@@ -196,7 +196,7 @@
     <t>Found 5 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:17.276Z</t>
+    <t>2026-06-13T08:46:40.482Z</t>
   </si>
   <si>
     <t>Validation</t>
@@ -208,7 +208,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:17.311Z</t>
+    <t>2026-06-13T08:46:40.526Z</t>
   </si>
   <si>
     <t>No results</t>
@@ -217,7 +217,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:18.644Z</t>
+    <t>2026-06-13T08:46:41.952Z</t>
   </si>
   <si>
     <t>Analytics route</t>
@@ -226,7 +226,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:18.724Z</t>
+    <t>2026-06-13T08:46:42.062Z</t>
   </si>
   <si>
     <t>Mobile layout</t>
@@ -235,7 +235,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:20.299Z</t>
+    <t>2026-06-13T08:46:43.675Z</t>
   </si>
   <si>
     <t>Desktop layout</t>
@@ -244,7 +244,7 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:21.138Z</t>
+    <t>2026-06-13T08:46:44.824Z</t>
   </si>
   <si>
     <t>API works</t>
@@ -253,7 +253,7 @@
     <t>100 jobs returned</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:21.983Z</t>
+    <t>2026-06-13T08:46:46.203Z</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -268,7 +268,7 @@
     <t>Page refresh succeeds</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:22.316Z</t>
+    <t>2026-06-13T08:46:46.643Z</t>
   </si>
   <si>
     <t>SPA routing</t>
@@ -277,7 +277,7 @@
     <t>Client-side routing</t>
   </si>
   <si>
-    <t>2026-06-13T08:19:23.320Z</t>
+    <t>2026-06-13T08:46:47.652Z</t>
   </si>
   <si>
     <t>Static ready</t>

--- a/tests/report/selenium-test-results.xlsx
+++ b/tests/report/selenium-test-results.xlsx
@@ -43,7 +43,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:34.374Z</t>
+    <t>2026-06-13T09:06:05.128Z</t>
   </si>
   <si>
     <t>Preview works</t>
@@ -52,7 +52,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:34.385Z</t>
+    <t>2026-06-13T09:06:05.142Z</t>
   </si>
   <si>
     <t>HTTPS backend</t>
@@ -67,7 +67,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.228Z</t>
+    <t>2026-06-13T09:06:07.726Z</t>
   </si>
   <si>
     <t>UI/UX</t>
@@ -79,7 +79,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.255Z</t>
+    <t>2026-06-13T09:06:07.743Z</t>
   </si>
   <si>
     <t>Features render</t>
@@ -88,7 +88,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.279Z</t>
+    <t>2026-06-13T09:06:07.763Z</t>
   </si>
   <si>
     <t>CTAs visible</t>
@@ -97,7 +97,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.305Z</t>
+    <t>2026-06-13T09:06:07.799Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -106,7 +106,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.327Z</t>
+    <t>2026-06-13T09:06:07.821Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -118,7 +118,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:37.642Z</t>
+    <t>2026-06-13T09:06:08.067Z</t>
   </si>
   <si>
     <t>Dashboard route</t>
@@ -133,7 +133,7 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:38.259Z</t>
+    <t>2026-06-13T09:06:08.519Z</t>
   </si>
   <si>
     <t>Dashboard cards</t>
@@ -142,7 +142,7 @@
     <t>Found 20 cards</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:38.286Z</t>
+    <t>2026-06-13T09:06:08.540Z</t>
   </si>
   <si>
     <t>Jobs route</t>
@@ -151,7 +151,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:38.765Z</t>
+    <t>2026-06-13T09:06:08.807Z</t>
   </si>
   <si>
     <t>Search input</t>
@@ -160,7 +160,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:39.175Z</t>
+    <t>2026-06-13T09:06:09.089Z</t>
   </si>
   <si>
     <t>Filters visible</t>
@@ -169,7 +169,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:39.204Z</t>
+    <t>2026-06-13T09:06:09.102Z</t>
   </si>
   <si>
     <t>Search works</t>
@@ -178,7 +178,7 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:40.426Z</t>
+    <t>2026-06-13T09:06:10.394Z</t>
   </si>
   <si>
     <t>Job grid</t>
@@ -187,7 +187,7 @@
     <t>Found 5 jobs</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:40.458Z</t>
+    <t>2026-06-13T09:06:10.419Z</t>
   </si>
   <si>
     <t>Apply buttons</t>
@@ -196,7 +196,7 @@
     <t>Found 5 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:40.482Z</t>
+    <t>2026-06-13T09:06:10.433Z</t>
   </si>
   <si>
     <t>Validation</t>
@@ -208,7 +208,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:40.526Z</t>
+    <t>2026-06-13T09:06:10.466Z</t>
   </si>
   <si>
     <t>No results</t>
@@ -217,7 +217,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:41.952Z</t>
+    <t>2026-06-13T09:06:11.842Z</t>
   </si>
   <si>
     <t>Analytics route</t>
@@ -226,7 +226,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:42.062Z</t>
+    <t>2026-06-13T09:06:11.956Z</t>
   </si>
   <si>
     <t>Mobile layout</t>
@@ -235,7 +235,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:43.675Z</t>
+    <t>2026-06-13T09:06:13.568Z</t>
   </si>
   <si>
     <t>Desktop layout</t>
@@ -244,7 +244,7 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:44.824Z</t>
+    <t>2026-06-13T09:06:14.757Z</t>
   </si>
   <si>
     <t>API works</t>
@@ -253,7 +253,7 @@
     <t>100 jobs returned</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:46.203Z</t>
+    <t>2026-06-13T09:06:15.182Z</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -268,7 +268,7 @@
     <t>Page refresh succeeds</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:46.643Z</t>
+    <t>2026-06-13T09:06:16.120Z</t>
   </si>
   <si>
     <t>SPA routing</t>
@@ -277,7 +277,7 @@
     <t>Client-side routing</t>
   </si>
   <si>
-    <t>2026-06-13T08:46:47.652Z</t>
+    <t>2026-06-13T09:06:17.121Z</t>
   </si>
   <si>
     <t>Static ready</t>

--- a/tests/report/selenium-test-results.xlsx
+++ b/tests/report/selenium-test-results.xlsx
@@ -43,7 +43,7 @@
     <t>Vite build configured</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:05.128Z</t>
+    <t>2026-06-15T05:10:42.355Z</t>
   </si>
   <si>
     <t>Preview works</t>
@@ -52,7 +52,7 @@
     <t>Vite preview available</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:05.142Z</t>
+    <t>2026-06-15T05:10:42.356Z</t>
   </si>
   <si>
     <t>HTTPS backend</t>
@@ -67,7 +67,7 @@
     <t>Home page rendered</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:07.726Z</t>
+    <t>2026-06-15T05:10:55.691Z</t>
   </si>
   <si>
     <t>UI/UX</t>
@@ -79,7 +79,7 @@
     <t>Found 1 headings</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:07.743Z</t>
+    <t>2026-06-15T05:10:55.702Z</t>
   </si>
   <si>
     <t>Features render</t>
@@ -88,7 +88,7 @@
     <t>Found 10 features</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:07.763Z</t>
+    <t>2026-06-15T05:10:55.713Z</t>
   </si>
   <si>
     <t>CTAs visible</t>
@@ -97,7 +97,7 @@
     <t>Found 2 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:07.799Z</t>
+    <t>2026-06-15T05:10:55.720Z</t>
   </si>
   <si>
     <t>Hero CTAs</t>
@@ -106,7 +106,7 @@
     <t>Found 2 hero actions</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:07.821Z</t>
+    <t>2026-06-15T05:10:55.731Z</t>
   </si>
   <si>
     <t>Functional</t>
@@ -118,7 +118,7 @@
     <t>Home loads</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:08.067Z</t>
+    <t>2026-06-15T05:10:55.834Z</t>
   </si>
   <si>
     <t>Dashboard route</t>
@@ -133,16 +133,16 @@
     <t>Found 3 nav items</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:08.519Z</t>
+    <t>2026-06-15T05:10:56.084Z</t>
   </si>
   <si>
     <t>Dashboard cards</t>
   </si>
   <si>
-    <t>Found 20 cards</t>
-  </si>
-  <si>
-    <t>2026-06-13T09:06:08.540Z</t>
+    <t>Found 16 cards</t>
+  </si>
+  <si>
+    <t>2026-06-15T05:10:56.092Z</t>
   </si>
   <si>
     <t>Jobs route</t>
@@ -151,7 +151,7 @@
     <t>Jobs page loaded</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:08.807Z</t>
+    <t>2026-06-15T05:10:56.149Z</t>
   </si>
   <si>
     <t>Search input</t>
@@ -160,7 +160,7 @@
     <t>Search field found</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:09.089Z</t>
+    <t>2026-06-15T05:10:57.612Z</t>
   </si>
   <si>
     <t>Filters visible</t>
@@ -169,7 +169,7 @@
     <t>Found 2 filters</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:09.102Z</t>
+    <t>2026-06-15T05:10:57.621Z</t>
   </si>
   <si>
     <t>Search works</t>
@@ -178,7 +178,7 @@
     <t>Query entered</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:10.394Z</t>
+    <t>2026-06-15T05:10:58.638Z</t>
   </si>
   <si>
     <t>Job grid</t>
@@ -187,7 +187,7 @@
     <t>Found 5 jobs</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:10.419Z</t>
+    <t>2026-06-15T05:10:58.648Z</t>
   </si>
   <si>
     <t>Apply buttons</t>
@@ -196,7 +196,7 @@
     <t>Found 5 buttons</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:10.433Z</t>
+    <t>2026-06-15T05:10:58.655Z</t>
   </si>
   <si>
     <t>Validation</t>
@@ -208,7 +208,7 @@
     <t>Search cleared</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:10.466Z</t>
+    <t>2026-06-15T05:10:58.671Z</t>
   </si>
   <si>
     <t>No results</t>
@@ -217,7 +217,7 @@
     <t>0 items</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:11.842Z</t>
+    <t>2026-06-15T05:10:59.741Z</t>
   </si>
   <si>
     <t>Analytics route</t>
@@ -226,7 +226,7 @@
     <t>Analytics loaded</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:11.956Z</t>
+    <t>2026-06-15T05:10:59.962Z</t>
   </si>
   <si>
     <t>Mobile layout</t>
@@ -235,7 +235,7 @@
     <t>Resized to mobile</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:13.568Z</t>
+    <t>2026-06-15T05:11:01.536Z</t>
   </si>
   <si>
     <t>Desktop layout</t>
@@ -244,7 +244,7 @@
     <t>Resized back to desktop</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:14.757Z</t>
+    <t>2026-06-15T05:11:02.368Z</t>
   </si>
   <si>
     <t>API works</t>
@@ -253,7 +253,7 @@
     <t>100 jobs returned</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:15.182Z</t>
+    <t>2026-06-15T05:11:03.272Z</t>
   </si>
   <si>
     <t>Navigation</t>
@@ -268,7 +268,7 @@
     <t>Page refresh succeeds</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:16.120Z</t>
+    <t>2026-06-15T05:11:03.462Z</t>
   </si>
   <si>
     <t>SPA routing</t>
@@ -277,7 +277,7 @@
     <t>Client-side routing</t>
   </si>
   <si>
-    <t>2026-06-13T09:06:17.121Z</t>
+    <t>2026-06-15T05:11:04.462Z</t>
   </si>
   <si>
     <t>Static ready</t>
